--- a/preprocess/resultados_sem_outlier_etcc.xlsx
+++ b/preprocess/resultados_sem_outlier_etcc.xlsx
@@ -47,6 +47,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P_px_V" sheetId="38" state="visible" r:id="rId38"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alvo_px_H" sheetId="39" state="visible" r:id="rId39"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="alvo_px_V" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NC_ER2sub" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="time2Sub_NC" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36508,6 +36510,2056 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fator_Lesao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Fator_ETCC</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ME_pre</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MD_pre</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ME_pos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MD_pos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.158706666666667</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.122938665734294</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.081891385767791</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.940223021582734</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.151688372093023</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.856112</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.063914179104477</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.869300653594771</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9160030581039756</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.455939698492463</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9926992753623189</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.415220385674931</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3450150375939846</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.255442857142858</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5461609195402297</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.662883620689656</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.259130769230769</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.12599173553719</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.98216875</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.745999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9291311475409837</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.8722711864406781</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.288866666666667</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7304919786096258</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.9862359550561796</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.345483050847457</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.135013888888889</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.253598944591029</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.399985611510792</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.375844086021505</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.739904347826087</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.066472222222222</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.595118483412322</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.442680232558139</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.033241610738255</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.957659459459459</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.072730769230769</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.172145390070921</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9596190476190477</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.8814375</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.799444444444444</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.428131578947368</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.86322972972973</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.621365187713311</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>1.965178082191781</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.341988636363636</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.504177777777778</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.207547008547009</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.258670781893005</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.136022421524664</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.767828125000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.04069964664311</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.911265734265734</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.269999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.982797814207651</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.031836257309941</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.046470833333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.408252427184466</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.909022875816994</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>2.112039215686275</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.183356223175966</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.23444578313253</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.191207792207792</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.931447811447811</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.916330508474578</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.755642857142858</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.477522580645161</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.115341085271318</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.387898734177215</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.279829545454545</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.235654761904762</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.516191616766467</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.59204347826087</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.479329787234043</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.277471428571429</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.038992366412214</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.311336538461539</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.011497835497836</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.533491071428572</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.9609308176100628</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.966875</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.190425925925926</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.967922155688623</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.4112451361867704</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.360553191489364</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.385057142857143</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.138695652173914</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.179302816901409</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.762872549019608</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.929999999999999</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>0.9792261904761907</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.081137254901961</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>1.507625</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.913144329896907</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>1.794619289340101</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.483861471861472</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>1.485720430107527</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.971423529411765</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>1.818139393939394</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.689185628742515</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>1.541064</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.775931623931625</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>1.299643442622952</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.429983122362869</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>1.493762886597939</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.908657370517928</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>1.187213058419244</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.151445614035087</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>1.454203703703704</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.368851428571429</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>1.343192513368984</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.272086206896552</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>1.285951417004049</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.269956692913386</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>0.7387699115044246</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.816440559440561</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>1.182121527777778</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.052386363636364</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>2.311168539325842</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.480899628252788</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>1.550746478873241</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.1615</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fator_Lesao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Fator_ETCC</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ME_pre</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MD_pre</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ME_pos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MD_pos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>73.46666666666667</v>
+      </c>
+      <c r="E2" t="n">
+        <v>74.84609223027806</v>
+      </c>
+      <c r="F2" t="n">
+        <v>71.87265917602997</v>
+      </c>
+      <c r="G2" t="n">
+        <v>76.11510791366908</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>77.16279069767441</v>
+      </c>
+      <c r="E3" t="n">
+        <v>81.92</v>
+      </c>
+      <c r="F3" t="n">
+        <v>72.72388059701494</v>
+      </c>
+      <c r="G3" t="n">
+        <v>78.62745098039217</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>79.29663608562691</v>
+      </c>
+      <c r="E4" t="n">
+        <v>75.7537688442211</v>
+      </c>
+      <c r="F4" t="n">
+        <v>84.78260869565217</v>
+      </c>
+      <c r="G4" t="n">
+        <v>78.23691460055097</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>70.67669172932331</v>
+      </c>
+      <c r="E5" t="n">
+        <v>75.14285714285715</v>
+      </c>
+      <c r="F5" t="n">
+        <v>72.29885057471266</v>
+      </c>
+      <c r="G5" t="n">
+        <v>65.51724137931035</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>102.1538461538462</v>
+      </c>
+      <c r="E6" t="n">
+        <v>91.36363636363636</v>
+      </c>
+      <c r="F6" t="n">
+        <v>82.3125</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>77.29508196721311</v>
+      </c>
+      <c r="E7" t="n">
+        <v>96.4705882352941</v>
+      </c>
+      <c r="F7" t="n">
+        <v>78.47457627118644</v>
+      </c>
+      <c r="G7" t="n">
+        <v>79.22222222222223</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>93.79679144385025</v>
+      </c>
+      <c r="E8" t="n">
+        <v>86.90140845070422</v>
+      </c>
+      <c r="F8" t="n">
+        <v>82.07865168539325</v>
+      </c>
+      <c r="G8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="E9" t="n">
+        <v>83.43007915567281</v>
+      </c>
+      <c r="F9" t="n">
+        <v>92.5179856115108</v>
+      </c>
+      <c r="G9" t="n">
+        <v>86.0752688172043</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>82.86956521739128</v>
+      </c>
+      <c r="E10" t="n">
+        <v>74.9074074074074</v>
+      </c>
+      <c r="F10" t="n">
+        <v>84.64454976303318</v>
+      </c>
+      <c r="G10" t="n">
+        <v>83.60465116279069</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>85.06711409395974</v>
+      </c>
+      <c r="E11" t="n">
+        <v>105.027027027027</v>
+      </c>
+      <c r="F11" t="n">
+        <v>74.82248520710058</v>
+      </c>
+      <c r="G11" t="n">
+        <v>83.01418439716312</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>71.42857142857143</v>
+      </c>
+      <c r="E12" t="n">
+        <v>78.33333333333333</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="E13" t="n">
+        <v>60.82706766917293</v>
+      </c>
+      <c r="F13" t="n">
+        <v>68.44594594594594</v>
+      </c>
+      <c r="G13" t="n">
+        <v>63.75426621160408</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>74.38356164383562</v>
+      </c>
+      <c r="F14" t="n">
+        <v>82.17391304347827</v>
+      </c>
+      <c r="G14" t="n">
+        <v>89.52380952380952</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>81.53409090909092</v>
+      </c>
+      <c r="E15" t="n">
+        <v>84.26666666666665</v>
+      </c>
+      <c r="F15" t="n">
+        <v>77.69230769230769</v>
+      </c>
+      <c r="G15" t="n">
+        <v>81.1111111111111</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>87.66816143497759</v>
+      </c>
+      <c r="E16" t="n">
+        <v>90.52083333333334</v>
+      </c>
+      <c r="F16" t="n">
+        <v>77.70318021201412</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>70.3825136612022</v>
+      </c>
+      <c r="F17" t="n">
+        <v>72.51461988304092</v>
+      </c>
+      <c r="G17" t="n">
+        <v>70.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>84.75728155339806</v>
+      </c>
+      <c r="E18" t="n">
+        <v>65.22875816993465</v>
+      </c>
+      <c r="F18" t="n">
+        <v>80.27777777777777</v>
+      </c>
+      <c r="G18" t="n">
+        <v>73.4313725490196</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>79.27038626609442</v>
+      </c>
+      <c r="E19" t="n">
+        <v>84.97991967871486</v>
+      </c>
+      <c r="F19" t="n">
+        <v>83.16017316017316</v>
+      </c>
+      <c r="G19" t="n">
+        <v>72.62626262626262</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>89.49152542372882</v>
+      </c>
+      <c r="E20" t="n">
+        <v>76.38095238095238</v>
+      </c>
+      <c r="F20" t="n">
+        <v>89.67741935483869</v>
+      </c>
+      <c r="G20" t="n">
+        <v>85.4421768707483</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>90.23255813953489</v>
+      </c>
+      <c r="E21" t="n">
+        <v>89.28270042194093</v>
+      </c>
+      <c r="F21" t="n">
+        <v>81.36363636363636</v>
+      </c>
+      <c r="G21" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>90.95808383233533</v>
+      </c>
+      <c r="E22" t="n">
+        <v>85.43478260869566</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>82.35714285714285</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SHAM</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>84.35114503816794</v>
+      </c>
+      <c r="E23" t="n">
+        <v>89.6153846153846</v>
+      </c>
+      <c r="F23" t="n">
+        <v>74.06926406926407</v>
+      </c>
+      <c r="G23" t="n">
+        <v>83.48214285714288</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>69.0566037735849</v>
+      </c>
+      <c r="E24" t="n">
+        <v>84.1875</v>
+      </c>
+      <c r="F24" t="n">
+        <v>80.8641975308642</v>
+      </c>
+      <c r="G24" t="n">
+        <v>79.16167664670658</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lesao_D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>61.55642023346304</v>
+      </c>
+      <c r="E25" t="n">
+        <v>69.36170212765958</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Lesao_E</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ETCC</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>71.77142857142859</v>
+      </c>
+      <c r="E26" t="n">
+        <v>83.69565217391302</v>
+      </c>
+      <c r="F26" t="n">
+        <v>72.53521126760563</v>
+      </c>
+      <c r="G26" t="n">
+        <v>68.52941176470588</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>64.54545454545452</v>
+      </c>
+      <c r="E27" t="n">
+        <v>55.71428571428572</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>92.85714285714288</v>
+      </c>
+      <c r="E28" t="n">
+        <v>83.72549019607845</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>89.58762886597937</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>91.67512690355329</v>
+      </c>
+      <c r="E30" t="n">
+        <v>82.64069264069263</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>94.40860215053762</v>
+      </c>
+      <c r="E31" t="n">
+        <v>99.94117647058823</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>99.57575757575756</v>
+      </c>
+      <c r="E32" t="n">
+        <v>89.88023952095809</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="E33" t="n">
+        <v>110.2564102564102</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>80.86065573770492</v>
+      </c>
+      <c r="E34" t="n">
+        <v>86.54008438818566</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>81.39175257731959</v>
+      </c>
+      <c r="E35" t="n">
+        <v>70.51792828685259</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>79.65635738831615</v>
+      </c>
+      <c r="E36" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>84.75308641975309</v>
+      </c>
+      <c r="E37" t="n">
+        <v>91.77142857142856</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>89.35828877005348</v>
+      </c>
+      <c r="E38" t="n">
+        <v>84.78448275862068</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>83.92712550607287</v>
+      </c>
+      <c r="E39" t="n">
+        <v>85</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>79.38053097345133</v>
+      </c>
+      <c r="E40" t="n">
+        <v>92.16783216783217</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>80.17361111111111</v>
+      </c>
+      <c r="E41" t="n">
+        <v>79.92424242424244</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>84.9438202247191</v>
+      </c>
+      <c r="E42" t="n">
+        <v>71.11524163568774</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>sem_lesao</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>82.04225352112677</v>
+      </c>
+      <c r="E43" t="n">
+        <v>80.23255813953489</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
